--- a/physical_location_labelling/physical_location_by_context/v04_verb-case_pattern/results/qualitative_analysis.xlsx
+++ b/physical_location_labelling/physical_location_by_context/v04_verb-case_pattern/results/qualitative_analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eestikeeleinstituut-my.sharepoint.com/personal/kertu_saul_eki_ee/Documents/Dokumendid/doktoritoo/estnltk_syntax_repo_kloon/physical_location_labelling/physical_location_by_context/results/v04_rulebased_annotation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eestikeeleinstituut-my.sharepoint.com/personal/kertu_saul_eki_ee/Documents/Dokumendid/doktoritoo/estnltk_syntax_repo_kloon/physical_location_labelling/physical_location_by_context/v04_verb-case_pattern/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="894" documentId="8_{942E2750-F767-4194-8FEF-6E12BC5E5D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04B5CB62-0A65-48B6-9B3C-86990ED68B69}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C0C81B5A-A434-4DEF-9260-7D04C9239187}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{C0C81B5A-A434-4DEF-9260-7D04C9239187}"/>
   </bookViews>
   <sheets>
     <sheet name="annotated_semtype_stats" sheetId="2" r:id="rId1"/>
@@ -658,10 +658,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1013,26 +1009,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8079E168-427D-4037-86F2-D75CA23ECFF3}">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.26953125" customWidth="1"/>
-    <col min="3" max="3" width="11.26953125" customWidth="1"/>
-    <col min="6" max="6" width="25.36328125" customWidth="1"/>
-    <col min="7" max="8" width="14.26953125" customWidth="1"/>
-    <col min="9" max="9" width="15.26953125" customWidth="1"/>
-    <col min="10" max="10" width="9.453125" customWidth="1"/>
-    <col min="11" max="11" width="8.26953125" customWidth="1"/>
+    <col min="1" max="1" width="12.23046875" customWidth="1"/>
+    <col min="3" max="3" width="11.23046875" customWidth="1"/>
+    <col min="6" max="6" width="25.3828125" customWidth="1"/>
+    <col min="7" max="8" width="14.23046875" customWidth="1"/>
+    <col min="9" max="9" width="15.23046875" customWidth="1"/>
+    <col min="10" max="10" width="9.4609375" customWidth="1"/>
+    <col min="11" max="11" width="8.23046875" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
     <col min="15" max="15" width="11" style="7" customWidth="1"/>
-    <col min="16" max="16" width="8.81640625" style="7" customWidth="1"/>
-    <col min="17" max="18" width="9.26953125" style="7"/>
-    <col min="19" max="19" width="14.54296875" style="7" customWidth="1"/>
-    <col min="20" max="20" width="31.26953125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="44.6328125" customWidth="1"/>
-    <col min="22" max="22" width="21.36328125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.84375" style="7" customWidth="1"/>
+    <col min="17" max="18" width="9.23046875" style="7"/>
+    <col min="19" max="19" width="14.53515625" style="7" customWidth="1"/>
+    <col min="20" max="20" width="31.23046875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="44.61328125" customWidth="1"/>
+    <col min="22" max="22" width="21.3828125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1100,7 +1096,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="145" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" ht="145.75" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1168,7 +1164,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1236,7 +1232,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1304,7 +1300,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" ht="160.30000000000001" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1372,7 +1368,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1440,7 +1436,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" ht="131.15" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1508,7 +1504,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="145" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" ht="160.30000000000001" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -1576,7 +1572,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" ht="131.15" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -1644,7 +1640,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="116" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" ht="116.6" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -1712,7 +1708,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="116" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" ht="116.6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>69</v>
       </c>
@@ -1777,7 +1773,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>70</v>
       </c>
@@ -1842,7 +1838,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" ht="131.15" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -1907,7 +1903,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" ht="189.45" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>78</v>
       </c>
@@ -1972,7 +1968,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" ht="102" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>79</v>
       </c>
@@ -2037,7 +2033,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="116" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" ht="116.6" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -2102,7 +2098,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>83</v>
       </c>
@@ -2167,7 +2163,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -2232,7 +2228,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" ht="131.15" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -2297,7 +2293,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>86</v>
       </c>
@@ -2362,7 +2358,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>87</v>
       </c>
@@ -2427,7 +2423,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>88</v>
       </c>
@@ -2564,21 +2560,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6C9021-B322-461B-9E7F-1CE10B2D779B}">
   <dimension ref="A1:S22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="6.1796875" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" customWidth="1"/>
-    <col min="4" max="4" width="6.7265625" customWidth="1"/>
-    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="2" max="2" width="6.15234375" customWidth="1"/>
+    <col min="3" max="3" width="7.15234375" customWidth="1"/>
+    <col min="4" max="4" width="6.69140625" customWidth="1"/>
+    <col min="5" max="5" width="6.61328125" customWidth="1"/>
     <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="10.1796875" customWidth="1"/>
+    <col min="7" max="7" width="10.15234375" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="20.1796875" customWidth="1"/>
+    <col min="9" max="9" width="20.15234375" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="19" max="19" width="13.1796875" customWidth="1"/>
+    <col min="19" max="19" width="13.15234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2637,7 +2633,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2675,7 +2671,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="5"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2713,7 +2709,7 @@
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2742,7 +2738,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2771,7 +2767,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2800,7 +2796,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2829,7 +2825,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -2858,7 +2854,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -2887,7 +2883,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -2916,7 +2912,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>69</v>
       </c>
@@ -2945,7 +2941,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>70</v>
       </c>
@@ -2974,7 +2970,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
         <v>72</v>
       </c>
@@ -3003,7 +2999,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
         <v>78</v>
       </c>
@@ -3032,7 +3028,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
         <v>79</v>
       </c>
@@ -3061,7 +3057,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
         <v>80</v>
       </c>
@@ -3090,7 +3086,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
         <v>83</v>
       </c>
@@ -3119,7 +3115,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
         <v>84</v>
       </c>
@@ -3148,7 +3144,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
         <v>85</v>
       </c>
@@ -3177,7 +3173,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
         <v>86</v>
       </c>
@@ -3206,7 +3202,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" s="8" t="s">
         <v>87</v>
       </c>
@@ -3235,7 +3231,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" s="10" t="s">
         <v>88</v>
       </c>
